--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484555_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484555_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5766</v>
+        <v>0.7718</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9491</v>
+        <v>2.0453</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3726</v>
+        <v>-1.2735</v>
       </c>
       <c r="G2" t="n">
         <v>-0.2219</v>
@@ -610,13 +610,13 @@
         <v>1.0995</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9241</v>
+        <v>-0.7289</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4774</v>
+        <v>-0.3812</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4468</v>
+        <v>-0.3477</v>
       </c>
       <c r="V2" t="n">
         <v>0.6231</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1842</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.9252</v>
+        <v>-1.0214</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1094</v>
+        <v>1.0846</v>
       </c>
       <c r="G3" t="n">
         <v>-1.0633</v>
@@ -688,13 +688,13 @@
         <v>1.0995</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1479</v>
+        <v>0.027</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2738</v>
+        <v>0.1776</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1259</v>
+        <v>-0.1506</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. LLOPIS FELIPO</t>
+          <t>L. HYLLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.6838</v>
+        <v>-1.6067</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0042</v>
+        <v>2.9426</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.6796</v>
+        <v>-4.5493</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.9048</v>
+        <v>-3.9296</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3053</v>
+        <v>-3.9134</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.5995</v>
+        <v>-0.0162</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5101</v>
+        <v>1.2284</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0837</v>
+        <v>-1.4804</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5736</v>
+        <v>2.7088</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.4149</v>
+        <v>-5.1581</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.389</v>
+        <v>-2.433</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0259</v>
+        <v>-2.725</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1833</v>
+        <v>1.4661</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.733</v>
+        <v>1.4661</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4043</v>
+        <v>0.2234</v>
       </c>
       <c r="T4" t="n">
-        <v>0.402</v>
+        <v>0.4472</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0023</v>
+        <v>-0.2238</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.6335</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. HYLLA</t>
+          <t>H. HINAREJOS GOMEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.0825</v>
+        <v>-1.8683</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6402</v>
+        <v>-0.1867</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.7227</v>
+        <v>-1.6816</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.9296</v>
+        <v>-2.3312</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.9134</v>
+        <v>-0.2891</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0162</v>
+        <v>-2.042</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2284</v>
+        <v>-0.5343</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.4804</v>
+        <v>0.065</v>
       </c>
       <c r="L5" t="n">
-        <v>2.7088</v>
+        <v>-0.5994</v>
       </c>
       <c r="M5" t="n">
-        <v>-5.1581</v>
+        <v>-1.7968</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.433</v>
+        <v>-0.3541</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.725</v>
+        <v>-1.4427</v>
       </c>
       <c r="P5" t="n">
-        <v>1.4661</v>
+        <v>0.1833</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4661</v>
+        <v>0.1833</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2524</v>
+        <v>0.2796</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1448</v>
+        <v>0.3477</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3972</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. HINAREJOS GOMEZ</t>
+          <t>V. LLOPIS FELIPO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,58 +877,58 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.3878</v>
+        <v>-1.942</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6814</v>
+        <v>-0.2376</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7064</v>
+        <v>-1.7044</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.3312</v>
+        <v>-1.9048</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2891</v>
+        <v>-0.3053</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.042</v>
+        <v>-1.5995</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5343</v>
+        <v>0.5101</v>
       </c>
       <c r="K6" t="n">
-        <v>0.065</v>
+        <v>1.0837</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5994</v>
+        <v>-0.5736</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.7968</v>
+        <v>-2.4149</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3541</v>
+        <v>-1.389</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.4427</v>
+        <v>-1.0259</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1833</v>
+        <v>-0.1833</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1833</v>
+        <v>0.733</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2399</v>
+        <v>0.1461</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1471</v>
+        <v>0.1686</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.09279999999999999</v>
+        <v>-0.0224</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. GARCIA SAHUQUILLO</t>
+          <t>M. AROCA RUBIO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.3307</v>
+        <v>-3.0099</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2972</v>
+        <v>-1.1355</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.6279</v>
+        <v>-1.8744</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.6538</v>
+        <v>-3.0979</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.2533</v>
+        <v>-1.1968</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4005</v>
+        <v>-1.9011</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2738</v>
+        <v>-0.6827</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.1211</v>
+        <v>-0.8334</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3949</v>
+        <v>0.1508</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.9276</v>
+        <v>-2.4152</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.1321</v>
+        <v>-0.3633</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7955</v>
+        <v>-2.0519</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.0158</v>
+        <v>-0.733</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.6651</v>
+        <v>-1.8326</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6493</v>
+        <v>1.0995</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1715</v>
+        <v>-0.4355</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5656</v>
+        <v>0.1128</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3941</v>
+        <v>-0.5483</v>
       </c>
       <c r="V7" t="n">
-        <v>3.1674</v>
+        <v>1.2566</v>
       </c>
       <c r="W7" t="n">
-        <v>4.1229</v>
+        <v>1.267</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9554</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. AROCA RUBIO</t>
+          <t>C. GARCIA SAHUQUILLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.3593</v>
+        <v>-3.5259</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2867</v>
+        <v>1.201</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0726</v>
+        <v>-4.727</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.0979</v>
+        <v>-4.6538</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1968</v>
+        <v>-4.2533</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.9011</v>
+        <v>-0.4005</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6827</v>
+        <v>0.2738</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8334</v>
+        <v>-1.1211</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1508</v>
+        <v>1.3949</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.4152</v>
+        <v>-4.9276</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3633</v>
+        <v>-3.1321</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.0519</v>
+        <v>-1.7955</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.733</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8326</v>
+        <v>-3.6651</v>
       </c>
       <c r="R8" t="n">
-        <v>1.0995</v>
+        <v>1.6493</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7849</v>
+        <v>-0.0237</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0384</v>
+        <v>0.4695</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7465000000000001</v>
+        <v>-0.4932</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2566</v>
+        <v>3.1674</v>
       </c>
       <c r="W8" t="n">
-        <v>1.267</v>
+        <v>4.1229</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.0104</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.9831</v>
+        <v>-4.2387</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1684</v>
+        <v>1.0862</v>
       </c>
       <c r="F9" t="n">
-        <v>-5.1515</v>
+        <v>-5.3249</v>
       </c>
       <c r="G9" t="n">
         <v>-3.6863</v>
@@ -1156,13 +1156,13 @@
         <v>1.4661</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2627</v>
+        <v>-0.5183</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0151</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2778</v>
+        <v>-0.4512</v>
       </c>
       <c r="V9" t="n">
         <v>0.3324</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. CHALER ROMERO</t>
+          <t>N. RAMON ANIBARRO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.938</v>
+        <v>-4.894</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.0696</v>
+        <v>-3.0392</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8683</v>
+        <v>-1.8548</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.943</v>
+        <v>-4.6106</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4427</v>
+        <v>-3.6585</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5003</v>
+        <v>-0.9520999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7137</v>
+        <v>-3.0275</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2075</v>
+        <v>-1.7871</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5062</v>
+        <v>-1.2404</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2293</v>
+        <v>-1.5831</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2351</v>
+        <v>-1.8713</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9941</v>
+        <v>0.2882</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.3823</v>
+        <v>0.3665</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.6651</v>
+        <v>-0.9163</v>
       </c>
       <c r="R10" t="n">
         <v>1.2828</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6127</v>
+        <v>-0.9719</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3092</v>
+        <v>-0.6844</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9219000000000001</v>
+        <v>-0.2875</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.5889</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>N. RAMON ANIBARRO</t>
+          <t>J. CHALER ROMERO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.3064</v>
+        <v>-5.1684</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3277</v>
+        <v>-4.3992</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9787</v>
+        <v>-0.7693</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.6106</v>
+        <v>-1.943</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.6585</v>
+        <v>-0.4427</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9520999999999999</v>
+        <v>-1.5003</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.0275</v>
+        <v>-0.7137</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.7871</v>
+        <v>-0.2075</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2404</v>
+        <v>-0.5062</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.5831</v>
+        <v>-1.2293</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.8713</v>
+        <v>-0.2351</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2882</v>
+        <v>-0.9941</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3665</v>
+        <v>-2.3823</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R11" t="n">
         <v>1.2828</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3842</v>
+        <v>-0.8431</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9728</v>
+        <v>-0.0203</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4114</v>
+        <v>-0.8228</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5889</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.763</v>
+        <v>-5.3759</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7193</v>
+        <v>-3.1835</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0438</v>
+        <v>-2.1924</v>
       </c>
       <c r="G12" t="n">
         <v>-6.2869</v>
@@ -1390,13 +1390,13 @@
         <v>1.0995</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5757</v>
+        <v>-0.1885</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6425</v>
+        <v>-0.1067</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0668</v>
+        <v>-0.0818</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.1253</v>
+        <v>-7.8538</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.7559</v>
+        <v>-4.2366</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.3694</v>
+        <v>-3.6172</v>
       </c>
       <c r="G13" t="n">
         <v>-3.034</v>
@@ -1468,13 +1468,13 @@
         <v>1.2828</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.09130000000000001</v>
+        <v>-0.8198</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3643</v>
+        <v>-0.1165</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.4555</v>
+        <v>-0.7033</v>
       </c>
       <c r="V13" t="n">
         <v>-2.5339</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-39.1991</v>
+        <v>-38.6486</v>
       </c>
       <c r="E14" t="n">
-        <v>-10.7151</v>
+        <v>-10.1646</v>
       </c>
       <c r="F14" t="n">
-        <v>-28.4841</v>
+        <v>-28.4842</v>
       </c>
       <c r="G14" t="n">
-        <v>-36.76330000000001</v>
+        <v>-36.7633</v>
       </c>
       <c r="H14" t="n">
         <v>-24.1004</v>
@@ -1519,7 +1519,7 @@
         <v>-12.6626</v>
       </c>
       <c r="J14" t="n">
-        <v>-5.102</v>
+        <v>-5.101999999999999</v>
       </c>
       <c r="K14" t="n">
         <v>-7.508299999999999</v>
@@ -1546,13 +1546,13 @@
         <v>13.7442</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.404200000000001</v>
+        <v>-3.8536</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2033999999999999</v>
+        <v>0.3471999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.2008</v>
+        <v>-4.200699999999999</v>
       </c>
       <c r="V14" t="n">
         <v>3.801</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10.9424</v>
+        <v>12.0628</v>
       </c>
       <c r="E15" t="n">
-        <v>8.527699999999999</v>
+        <v>8.9123</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4147</v>
+        <v>3.1505</v>
       </c>
       <c r="G15" t="n">
         <v>8.730399999999999</v>
@@ -1624,13 +1624,13 @@
         <v>2.1991</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6206</v>
+        <v>0.4998</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1666</v>
+        <v>0.218</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.4539</v>
+        <v>0.2818</v>
       </c>
       <c r="V15" t="n">
         <v>0.6335</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>9.0947</v>
+        <v>9.698</v>
       </c>
       <c r="E16" t="n">
         <v>6.256</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8387</v>
+        <v>3.442</v>
       </c>
       <c r="G16" t="n">
         <v>5.4163</v>
@@ -1702,13 +1702,13 @@
         <v>2.1991</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2124</v>
+        <v>0.8156</v>
       </c>
       <c r="T16" t="n">
         <v>0.6026</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3902</v>
+        <v>0.213</v>
       </c>
       <c r="V16" t="n">
         <v>1.267</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.9294</v>
+        <v>5.8571</v>
       </c>
       <c r="E17" t="n">
-        <v>4.7638</v>
+        <v>3.5138</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1656</v>
+        <v>2.3433</v>
       </c>
       <c r="G17" t="n">
         <v>4.4046</v>
@@ -1780,13 +1780,13 @@
         <v>0.9163</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5247</v>
+        <v>1.4525</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3801</v>
+        <v>1.1301</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1446</v>
+        <v>0.3224</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>5.6869</v>
+        <v>5.0953</v>
       </c>
       <c r="E18" t="n">
-        <v>4.2418</v>
+        <v>3.761</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4451</v>
+        <v>1.3343</v>
       </c>
       <c r="G18" t="n">
         <v>5.1174</v>
@@ -1858,13 +1858,13 @@
         <v>2.1991</v>
       </c>
       <c r="S18" t="n">
-        <v>1.724</v>
+        <v>1.1323</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8228</v>
+        <v>0.342</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9012</v>
+        <v>0.7903</v>
       </c>
       <c r="V18" t="n">
         <v>0.3115</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.742</v>
+        <v>3.0129</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8676</v>
+        <v>1.06</v>
       </c>
       <c r="F19" t="n">
-        <v>1.8743</v>
+        <v>1.953</v>
       </c>
       <c r="G19" t="n">
         <v>4.4259</v>
@@ -1936,13 +1936,13 @@
         <v>1.4661</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8659</v>
+        <v>1.1369</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5671</v>
+        <v>0.7594</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2988</v>
+        <v>0.3774</v>
       </c>
       <c r="V19" t="n">
         <v>-1.267</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. GADEA HIERRO</t>
+          <t>A. DE LA CAL DOMINGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4856</v>
+        <v>2.4803</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1918</v>
+        <v>1.4759</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2939</v>
+        <v>1.0044</v>
       </c>
       <c r="G20" t="n">
-        <v>2.0958</v>
+        <v>2.6249</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8011</v>
+        <v>0.9929</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7053</v>
+        <v>1.632</v>
       </c>
       <c r="J20" t="n">
-        <v>2.9234</v>
+        <v>2.2285</v>
       </c>
       <c r="K20" t="n">
-        <v>2.731</v>
+        <v>0.7245</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1925</v>
+        <v>1.5041</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8276</v>
+        <v>0.3964</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0701</v>
+        <v>0.2685</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8977000000000001</v>
+        <v>0.1279</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.733</v>
+        <v>0.9163</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.8326</v>
+        <v>-0.9163</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0995</v>
+        <v>1.8326</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4789</v>
+        <v>0.5281</v>
       </c>
       <c r="T20" t="n">
-        <v>0.457</v>
+        <v>0.1637</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0219</v>
+        <v>0.3644</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6439</v>
+        <v>-1.5889</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. DE LA CAL DOMINGUEZ</t>
+          <t>A. GADEA HIERRO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.1205</v>
+        <v>2.4695</v>
       </c>
       <c r="E21" t="n">
-        <v>1.4759</v>
+        <v>2.1918</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6446</v>
+        <v>0.2778</v>
       </c>
       <c r="G21" t="n">
-        <v>2.6249</v>
+        <v>2.0958</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9929</v>
+        <v>2.8011</v>
       </c>
       <c r="I21" t="n">
-        <v>1.632</v>
+        <v>-0.7053</v>
       </c>
       <c r="J21" t="n">
-        <v>2.2285</v>
+        <v>2.9234</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7245</v>
+        <v>2.731</v>
       </c>
       <c r="L21" t="n">
-        <v>1.5041</v>
+        <v>0.1925</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3964</v>
+        <v>-0.8276</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2685</v>
+        <v>0.0701</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1279</v>
+        <v>-0.8977000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9163</v>
+        <v>-0.733</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9163</v>
+        <v>-1.8326</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8326</v>
+        <v>1.0995</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1682</v>
+        <v>0.4629</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1637</v>
+        <v>0.457</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0046</v>
+        <v>0.0058</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.5889</v>
+        <v>0.6439</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.6439</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.5889</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.2623</v>
+        <v>1.9952</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2815</v>
+        <v>1.7623</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0192</v>
+        <v>0.2329</v>
       </c>
       <c r="G22" t="n">
         <v>1.0773</v>
@@ -2170,13 +2170,13 @@
         <v>1.2828</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1919</v>
+        <v>0.5409</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1267</v>
+        <v>0.6075</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3187</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>0.0104</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4187</v>
+        <v>1.2272</v>
       </c>
       <c r="E23" t="n">
-        <v>0.5286999999999999</v>
+        <v>1.1057</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1101</v>
+        <v>0.1216</v>
       </c>
       <c r="G23" t="n">
         <v>2.7927</v>
@@ -2248,13 +2248,13 @@
         <v>1.8326</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1621</v>
+        <v>0.6465</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5324</v>
+        <v>0.0445</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3703</v>
+        <v>0.602</v>
       </c>
       <c r="V23" t="n">
         <v>-2.212</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.4834</v>
+        <v>-2.1352</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6508</v>
+        <v>-1.5547</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8326</v>
+        <v>-0.5805</v>
       </c>
       <c r="G24" t="n">
         <v>0.07779999999999999</v>
@@ -2326,13 +2326,13 @@
         <v>0.5498</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5954</v>
+        <v>-0.2472</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2202</v>
+        <v>-0.1241</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3752</v>
+        <v>-0.1231</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5993</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>39.19909999999999</v>
+        <v>41.76310000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>28.484</v>
+        <v>28.4841</v>
       </c>
       <c r="F25" t="n">
-        <v>10.715</v>
+        <v>13.2793</v>
       </c>
       <c r="G25" t="n">
         <v>36.7631</v>
@@ -2389,7 +2389,7 @@
         <v>5.102</v>
       </c>
       <c r="N25" t="n">
-        <v>7.508100000000001</v>
+        <v>7.5081</v>
       </c>
       <c r="O25" t="n">
         <v>-2.4064</v>
@@ -2404,13 +2404,13 @@
         <v>15.577</v>
       </c>
       <c r="S25" t="n">
-        <v>4.404100000000001</v>
+        <v>6.968299999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>4.2008</v>
+        <v>4.2007</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2034</v>
+        <v>2.7674</v>
       </c>
       <c r="V25" t="n">
         <v>-3.8009</v>
